--- a/1. ELICITACION/1.5 Backlog/GN4_Backlog_PlantillaV1.xlsx
+++ b/1. ELICITACION/1.5 Backlog/GN4_Backlog_PlantillaV1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoshPC\Documents\Universidad\Analisis y Diseño\Unidad2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoshPC\Documents\Universidad\Analisis y Diseño\Github\YulianaValencia_30724_G4_ADSW\1. ELICITACION\1.5 Backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EC48BCC-D7FB-492E-A883-AFE35B0A16B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34386EB3-BD70-429B-8533-E78087825059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -520,24 +520,24 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -844,13 +844,13 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="9" t="s">
         <v>22</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -862,10 +862,10 @@
       <c r="F2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="9" t="s">
         <v>27</v>
       </c>
       <c r="I2" s="4"/>
@@ -888,16 +888,16 @@
       <c r="Z2" s="4"/>
     </row>
     <row r="3" spans="1:26" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="9" t="s">
         <v>31</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -906,24 +906,24 @@
       <c r="F3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="9" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="9" t="s">
         <v>37</v>
       </c>
       <c r="E4" s="3" t="s">
@@ -932,24 +932,24 @@
       <c r="F4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="9" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="9" t="s">
         <v>43</v>
       </c>
       <c r="E5" s="3" t="s">
@@ -958,10 +958,10 @@
       <c r="F5" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="9" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1985,31 +1985,31 @@
       </c>
     </row>
     <row r="3" spans="1:27" ht="26.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="10" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2093,18 +2093,18 @@
       <c r="B6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14" t="s">
+      <c r="D6" s="14"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14">
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11">
         <v>2</v>
       </c>
       <c r="K6" s="4"/>
@@ -2130,18 +2130,18 @@
       <c r="B7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14" t="s">
+      <c r="D7" s="14"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14">
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11">
         <v>3</v>
       </c>
       <c r="K7" s="4"/>
@@ -2167,18 +2167,18 @@
       <c r="B8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14" t="s">
+      <c r="D8" s="15"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14">
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11">
         <v>3</v>
       </c>
       <c r="K8" s="4"/>
@@ -2242,18 +2242,18 @@
       <c r="B11" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14" t="s">
+      <c r="D11" s="14"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14">
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2261,18 +2261,18 @@
       <c r="B12" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14" t="s">
+      <c r="D12" s="14"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14">
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2280,18 +2280,18 @@
       <c r="B13" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14" t="s">
+      <c r="D13" s="15"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14">
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2338,18 +2338,18 @@
       <c r="B16" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14" t="s">
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14">
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11">
         <v>3</v>
       </c>
     </row>
@@ -2357,18 +2357,18 @@
       <c r="B17" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14" t="s">
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14">
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11">
         <v>3</v>
       </c>
     </row>
@@ -2376,41 +2376,39 @@
       <c r="B18" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="14" t="s">
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="G18" s="14" t="s">
+      <c r="G18" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="H18" s="14">
+      <c r="I18" s="11"/>
+      <c r="J18" s="11">
         <v>4</v>
       </c>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
     </row>
     <row r="19" spans="2:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14" t="s">
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14">
+      <c r="H19" s="11"/>
+      <c r="J19" s="11">
         <v>2</v>
       </c>
-      <c r="J19" s="14"/>
     </row>
     <row r="20" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
@@ -2455,18 +2453,18 @@
       <c r="B22" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14" t="s">
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14">
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2474,18 +2472,18 @@
       <c r="B23" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14" t="s">
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14">
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11">
         <v>4</v>
       </c>
     </row>
@@ -2493,18 +2491,18 @@
       <c r="B24" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14" t="s">
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14">
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11">
         <v>4</v>
       </c>
     </row>
@@ -3422,19 +3420,19 @@
     <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C16:E16"/>
     <mergeCell ref="C24:E24"/>
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="C22:E22"/>
     <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
